--- a/CYP3A4/CYP3A4_Allele_def_rs_excluidos.xlsx
+++ b/CYP3A4/CYP3A4_Allele_def_rs_excluidos.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Fobos\Proyecto_Diana\TFM_GenoStaR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Fobos\Proyecto_Diana\TFM_GenoStaR\CYP3A4\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11160" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23010" windowHeight="9015" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Salida_R" sheetId="1" r:id="rId1"/>
@@ -1816,7 +1816,6 @@
         <v>96</v>
       </c>
       <c r="AA28">
-        <f>SUM(AA4:AA27)*100</f>
         <v>0.55205460000000017</v>
       </c>
     </row>

--- a/CYP3A4/CYP3A4_Allele_def_rs_excluidos.xlsx
+++ b/CYP3A4/CYP3A4_Allele_def_rs_excluidos.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23010" windowHeight="9015" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11160" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Salida_R" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="111">
   <si>
     <t>rsID</t>
   </si>
@@ -335,6 +335,24 @@
   </si>
   <si>
     <t>https://www.ncbi.nlm.nih.gov/snp/rs1318364992</t>
+  </si>
+  <si>
+    <t>Corresponde a rs2485908963 (CYP3A4_allele_definition_table-PS216409-1454596980)</t>
+  </si>
+  <si>
+    <t>dbSNP</t>
+  </si>
+  <si>
+    <t>https://www.ncbi.nlm.nih.gov/snp/rs2485908963</t>
+  </si>
+  <si>
+    <t>Corresponde a rs2485889420 (CYP3A4_allele_definition_table-PS216409-1454596980)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dbSNP </t>
+  </si>
+  <si>
+    <t>https://www.ncbi.nlm.nih.gov/snp/rs2485889420</t>
   </si>
 </sst>
 </file>
@@ -366,7 +384,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -397,6 +415,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -411,7 +435,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -423,6 +447,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1189,14 +1215,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD28"/>
+  <dimension ref="A1:AE28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="26" max="26" width="13.7109375" customWidth="1"/>
-    <col min="27" max="28" width="14.28515625" customWidth="1"/>
+    <col min="26" max="27" width="13.7109375" customWidth="1"/>
+    <col min="28" max="29" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1275,22 +1301,22 @@
       <c r="Z1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -1367,7 +1393,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -1377,17 +1403,17 @@
       <c r="Z4" t="s">
         <v>13</v>
       </c>
-      <c r="AA4">
+      <c r="AB4">
         <v>3.0519999999999999E-5</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>99</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -1397,17 +1423,17 @@
       <c r="Z5" t="s">
         <v>8</v>
       </c>
-      <c r="AA5">
+      <c r="AB5">
         <v>4.7840000000000001E-3</v>
       </c>
-      <c r="AB5" t="s">
+      <c r="AC5" t="s">
         <v>99</v>
       </c>
-      <c r="AC5" t="s">
+      <c r="AD5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>49</v>
       </c>
@@ -1417,17 +1443,17 @@
       <c r="Z6" t="s">
         <v>22</v>
       </c>
-      <c r="AA6">
+      <c r="AB6">
         <v>1.6950000000000001E-6</v>
       </c>
-      <c r="AB6" t="s">
+      <c r="AC6" t="s">
         <v>99</v>
       </c>
-      <c r="AC6" t="s">
+      <c r="AD6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>50</v>
       </c>
@@ -1437,17 +1463,17 @@
       <c r="Z7" t="s">
         <v>24</v>
       </c>
-      <c r="AA7">
+      <c r="AB7">
         <v>5.0600000000000005E-4</v>
       </c>
-      <c r="AB7" t="s">
+      <c r="AC7" t="s">
         <v>99</v>
       </c>
-      <c r="AC7" t="s">
+      <c r="AD7" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>51</v>
       </c>
@@ -1457,17 +1483,17 @@
       <c r="Z8" t="s">
         <v>14</v>
       </c>
-      <c r="AA8">
+      <c r="AB8">
         <v>0</v>
       </c>
-      <c r="AB8" t="s">
+      <c r="AC8" t="s">
         <v>99</v>
       </c>
-      <c r="AC8" t="s">
+      <c r="AD8" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>54</v>
       </c>
@@ -1477,17 +1503,17 @@
       <c r="Z9" t="s">
         <v>9</v>
       </c>
-      <c r="AA9">
+      <c r="AB9">
         <v>0</v>
       </c>
-      <c r="AB9" t="s">
+      <c r="AC9" t="s">
         <v>99</v>
       </c>
-      <c r="AC9" t="s">
+      <c r="AD9" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>55</v>
       </c>
@@ -1497,17 +1523,17 @@
       <c r="Z10" t="s">
         <v>10</v>
       </c>
-      <c r="AA10">
+      <c r="AB10">
         <v>3.2209999999999998E-5</v>
       </c>
-      <c r="AB10" t="s">
+      <c r="AC10" t="s">
         <v>99</v>
       </c>
-      <c r="AC10" t="s">
+      <c r="AD10" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>56</v>
       </c>
@@ -1517,17 +1543,17 @@
       <c r="Z11" t="s">
         <v>3</v>
       </c>
-      <c r="AA11">
+      <c r="AB11">
         <v>0</v>
       </c>
-      <c r="AB11" t="s">
+      <c r="AC11" t="s">
         <v>99</v>
       </c>
-      <c r="AC11" t="s">
+      <c r="AD11" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -1537,17 +1563,18 @@
       <c r="Z12" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="AA12">
+      <c r="AA12" s="8"/>
+      <c r="AB12">
         <v>0</v>
       </c>
-      <c r="AB12" t="s">
+      <c r="AC12" t="s">
         <v>100</v>
       </c>
-      <c r="AC12" s="3" t="s">
+      <c r="AD12" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>58</v>
       </c>
@@ -1557,17 +1584,17 @@
       <c r="Z13" t="s">
         <v>7</v>
       </c>
-      <c r="AA13">
+      <c r="AB13">
         <v>1.102E-5</v>
       </c>
-      <c r="AB13" t="s">
+      <c r="AC13" t="s">
         <v>99</v>
       </c>
-      <c r="AC13" t="s">
+      <c r="AD13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>59</v>
       </c>
@@ -1577,17 +1604,17 @@
       <c r="Z14" t="s">
         <v>15</v>
       </c>
-      <c r="AA14">
+      <c r="AB14">
         <v>0</v>
       </c>
-      <c r="AB14" t="s">
+      <c r="AC14" t="s">
         <v>99</v>
       </c>
-      <c r="AC14" t="s">
+      <c r="AD14" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -1597,17 +1624,17 @@
       <c r="Z15" t="s">
         <v>16</v>
       </c>
-      <c r="AA15">
+      <c r="AB15">
         <v>2.7970000000000002E-5</v>
       </c>
-      <c r="AB15" t="s">
+      <c r="AC15" t="s">
         <v>99</v>
       </c>
-      <c r="AC15" t="s">
+      <c r="AD15" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>61</v>
       </c>
@@ -1617,17 +1644,17 @@
       <c r="Z16" t="s">
         <v>18</v>
       </c>
-      <c r="AA16">
+      <c r="AB16">
         <v>5.6780000000000002E-5</v>
       </c>
-      <c r="AB16" t="s">
+      <c r="AC16" t="s">
         <v>99</v>
       </c>
-      <c r="AC16" t="s">
+      <c r="AD16" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>62</v>
       </c>
@@ -1637,17 +1664,17 @@
       <c r="Z17" t="s">
         <v>21</v>
       </c>
-      <c r="AA17">
+      <c r="AB17">
         <v>4.5769999999999997E-5</v>
       </c>
-      <c r="AB17" t="s">
+      <c r="AC17" t="s">
         <v>99</v>
       </c>
-      <c r="AC17" t="s">
+      <c r="AD17" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>63</v>
       </c>
@@ -1657,17 +1684,17 @@
       <c r="Z18" t="s">
         <v>2</v>
       </c>
-      <c r="AA18">
+      <c r="AB18">
         <v>2.1189999999999999E-5</v>
       </c>
-      <c r="AB18" t="s">
+      <c r="AC18" t="s">
         <v>99</v>
       </c>
-      <c r="AC18" t="s">
+      <c r="AD18" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>66</v>
       </c>
@@ -1677,17 +1704,17 @@
       <c r="Z19" t="s">
         <v>1</v>
       </c>
-      <c r="AA19">
+      <c r="AB19">
         <v>0</v>
       </c>
-      <c r="AB19" t="s">
+      <c r="AC19" t="s">
         <v>99</v>
       </c>
-      <c r="AC19" t="s">
+      <c r="AD19" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>67</v>
       </c>
@@ -1697,8 +1724,20 @@
       <c r="Z20" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AA20" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="AB20" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>106</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>68</v>
       </c>
@@ -1708,8 +1747,20 @@
       <c r="Z21" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AA21" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AB21" s="7">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>109</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>70</v>
       </c>
@@ -1719,17 +1770,18 @@
       <c r="Z22" t="s">
         <v>11</v>
       </c>
-      <c r="AA22">
+      <c r="AA22" s="8"/>
+      <c r="AB22">
         <v>3.3909999999999998E-6</v>
       </c>
-      <c r="AB22" t="s">
+      <c r="AC22" t="s">
         <v>99</v>
       </c>
-      <c r="AC22" t="s">
+      <c r="AD22" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>71</v>
       </c>
@@ -1739,17 +1791,18 @@
       <c r="Z23" t="s">
         <v>12</v>
       </c>
-      <c r="AA23">
+      <c r="AA23" s="8"/>
+      <c r="AB23">
         <v>0</v>
       </c>
-      <c r="AB23" t="s">
+      <c r="AC23" t="s">
         <v>99</v>
       </c>
-      <c r="AC23" t="s">
+      <c r="AD23" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>72</v>
       </c>
@@ -1759,8 +1812,9 @@
       <c r="Z24" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AA24" s="8"/>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>73</v>
       </c>
@@ -1770,17 +1824,18 @@
       <c r="Z25" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="AA25">
+      <c r="AA25" s="8"/>
+      <c r="AB25">
         <v>0</v>
       </c>
-      <c r="AB25" t="s">
+      <c r="AC25" t="s">
         <v>100</v>
       </c>
-      <c r="AC25" t="s">
+      <c r="AD25" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>74</v>
       </c>
@@ -1790,8 +1845,9 @@
       <c r="Z26" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AA26" s="8"/>
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>75</v>
       </c>
@@ -1801,27 +1857,28 @@
       <c r="Z27" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="AB27" t="s">
+      <c r="AA27" s="8"/>
+      <c r="AC27" t="s">
         <v>102</v>
       </c>
-      <c r="AC27" s="3" t="s">
+      <c r="AD27" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="AD27" t="s">
+      <c r="AE27" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="Z28" t="s">
         <v>96</v>
       </c>
-      <c r="AA28">
-        <v>0.55205460000000017</v>
+      <c r="AB28">
+        <v>0.55235460000000014</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="AC12" r:id="rId1"/>
+    <hyperlink ref="AD12" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CYP3A4/CYP3A4_Allele_def_rs_excluidos.xlsx
+++ b/CYP3A4/CYP3A4_Allele_def_rs_excluidos.xlsx
@@ -1873,7 +1873,7 @@
         <v>96</v>
       </c>
       <c r="AB28">
-        <v>0.55235460000000014</v>
+        <v>0.55235460000000003</v>
       </c>
     </row>
   </sheetData>
